--- a/common/template/document/tabel_teachers_extra_budget_half.xlsx
+++ b/common/template/document/tabel_teachers_extra_budget_half.xlsx
@@ -815,6 +815,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -846,38 +878,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1264,54 +1264,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="AG1" s="55"/>
-      <c r="AH1" s="55"/>
-      <c r="AI1" s="55"/>
-      <c r="AJ1" s="55"/>
-      <c r="AK1" s="55"/>
+      <c r="AG1" s="67"/>
+      <c r="AH1" s="67"/>
+      <c r="AI1" s="67"/>
+      <c r="AJ1" s="67"/>
+      <c r="AK1" s="67"/>
     </row>
     <row r="2" spans="1:46" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71"/>
     </row>
     <row r="3" spans="1:46" s="1" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="61" t="s">
+      <c r="E3" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="61"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="61"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="61"/>
-      <c r="U3" s="61"/>
-      <c r="V3" s="61"/>
-      <c r="W3" s="61"/>
-      <c r="X3" s="61"/>
-      <c r="Y3" s="61"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="73"/>
+      <c r="Y3" s="73"/>
       <c r="AI3" s="24" t="s">
         <v>16</v>
       </c>
@@ -1322,73 +1322,73 @@
       <c r="AE4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AI4" s="56" t="s">
+      <c r="AI4" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="AJ4" s="57"/>
-      <c r="AK4" s="58"/>
+      <c r="AJ4" s="69"/>
+      <c r="AK4" s="70"/>
     </row>
     <row r="5" spans="1:46" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G5" s="66" t="s">
+      <c r="G5" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="59"/>
+      <c r="U5" s="59"/>
+      <c r="V5" s="59"/>
+      <c r="W5" s="59"/>
+      <c r="X5" s="59"/>
+      <c r="Y5" s="59"/>
       <c r="AF5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AI5" s="52"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="54"/>
+      <c r="AI5" s="64"/>
+      <c r="AJ5" s="65"/>
+      <c r="AK5" s="66"/>
     </row>
     <row r="6" spans="1:46" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="D6" s="60" t="s">
+      <c r="B6" s="60"/>
+      <c r="D6" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="60"/>
-      <c r="T6" s="60"/>
-      <c r="U6" s="60"/>
-      <c r="V6" s="60"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="60"/>
-      <c r="Y6" s="60"/>
-      <c r="Z6" s="60"/>
-      <c r="AA6" s="60"/>
-      <c r="AB6" s="60"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="72"/>
+      <c r="Y6" s="72"/>
+      <c r="Z6" s="72"/>
+      <c r="AA6" s="72"/>
+      <c r="AB6" s="72"/>
       <c r="AF6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1402,69 +1402,69 @@
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="65" t="s">
+      <c r="D7" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="65"/>
-      <c r="M7" s="65"/>
-      <c r="N7" s="65"/>
-      <c r="O7" s="65"/>
-      <c r="P7" s="65"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="65"/>
-      <c r="S7" s="65"/>
-      <c r="T7" s="65"/>
-      <c r="U7" s="65"/>
-      <c r="V7" s="65"/>
-      <c r="W7" s="65"/>
-      <c r="X7" s="65"/>
-      <c r="Y7" s="65"/>
-      <c r="Z7" s="65"/>
-      <c r="AA7" s="65"/>
-      <c r="AB7" s="65"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="57"/>
+      <c r="P7" s="57"/>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="57"/>
+      <c r="S7" s="57"/>
+      <c r="T7" s="57"/>
+      <c r="U7" s="57"/>
+      <c r="V7" s="57"/>
+      <c r="W7" s="57"/>
+      <c r="X7" s="57"/>
+      <c r="Y7" s="57"/>
+      <c r="Z7" s="57"/>
+      <c r="AA7" s="57"/>
+      <c r="AB7" s="57"/>
       <c r="AI7" s="11"/>
       <c r="AJ7" s="12"/>
       <c r="AK7" s="13"/>
     </row>
     <row r="8" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="D8" s="71" t="s">
+      <c r="B8" s="60"/>
+      <c r="D8" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="71"/>
-      <c r="R8" s="71"/>
-      <c r="S8" s="71"/>
-      <c r="T8" s="71"/>
-      <c r="U8" s="71"/>
-      <c r="V8" s="71"/>
-      <c r="W8" s="71"/>
-      <c r="X8" s="71"/>
-      <c r="Y8" s="71"/>
-      <c r="Z8" s="71"/>
-      <c r="AA8" s="71"/>
-      <c r="AB8" s="71"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="63"/>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="63"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="63"/>
+      <c r="U8" s="63"/>
+      <c r="V8" s="63"/>
+      <c r="W8" s="63"/>
+      <c r="X8" s="63"/>
+      <c r="Y8" s="63"/>
+      <c r="Z8" s="63"/>
+      <c r="AA8" s="63"/>
+      <c r="AB8" s="63"/>
       <c r="AC8" s="1" t="s">
         <v>23</v>
       </c>
@@ -1483,11 +1483,11 @@
         <v>24</v>
       </c>
       <c r="AE9" s="14"/>
-      <c r="AI9" s="52" t="s">
+      <c r="AI9" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="AJ9" s="53"/>
-      <c r="AK9" s="54"/>
+      <c r="AJ9" s="65"/>
+      <c r="AK9" s="66"/>
     </row>
     <row r="10" spans="1:46" s="1" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20"/>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="11" spans="1:46" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="62"/>
       <c r="D11" s="15"/>
       <c r="E11" s="27"/>
       <c r="F11" s="19"/>
@@ -1584,10 +1584,10 @@
       <c r="A12" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="54" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="3"/>
@@ -1642,8 +1642,8 @@
       <c r="A13" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1694,8 +1694,8 @@
     </row>
     <row r="14" spans="1:46" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="17"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,8 +1810,8 @@
     </row>
     <row r="15" spans="1:46" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="17"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
       <c r="D15" s="3" t="s">
         <v>17</v>
       </c>
@@ -1864,8 +1864,8 @@
     </row>
     <row r="16" spans="1:46" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1916,8 +1916,8 @@
     </row>
     <row r="17" spans="1:46" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -2274,7 +2274,7 @@
       <c r="R21" s="46"/>
       <c r="S21" s="46"/>
       <c r="T21" s="50">
-        <f ca="1">SUMPRODUCT((T19                          : INDIRECT(ADDRESS( ROW()-1,COLUMN())))*ISODD(ROW(T19                          : INDIRECT(ADDRESS( ROW()-1,COLUMN())))))</f>
+        <f ca="1">SUMPRODUCT((T19                           : INDIRECT(ADDRESS( ROW()-1,COLUMN())))*ISODD(ROW(T19                           : INDIRECT(ADDRESS( ROW()-1,COLUMN())))))</f>
         <v>0</v>
       </c>
       <c r="U21" s="40"/>
@@ -2358,23 +2358,23 @@
       <c r="AK23" s="30"/>
     </row>
     <row r="24" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
       <c r="D24" s="23"/>
       <c r="E24" s="23"/>
       <c r="F24" s="23"/>
       <c r="G24" s="23"/>
-      <c r="H24" s="72" t="s">
+      <c r="H24" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="72"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
@@ -2407,35 +2407,35 @@
       <c r="D25" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="72" t="s">
+      <c r="H25" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="73"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="52"/>
       <c r="Q25" s="31"/>
       <c r="AK25" s="33"/>
     </row>
     <row r="26" spans="1:46" s="22" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="72" t="s">
+      <c r="A26" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="72"/>
-      <c r="C26" s="72"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
       <c r="F26" s="23"/>
       <c r="G26" s="23"/>
-      <c r="H26" s="72" t="s">
+      <c r="H26" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="52"/>
       <c r="Q26" s="31"/>
       <c r="R26" s="22" t="s">
         <v>80</v>
@@ -2458,14 +2458,14 @@
       <c r="D27" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="72" t="s">
+      <c r="H27" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="72"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
       <c r="Q27" s="31"/>
       <c r="S27" s="22" t="s">
         <v>81</v>
@@ -13498,6 +13498,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="AI9:AK9"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="H2:U2"/>
+    <mergeCell ref="D6:AB6"/>
+    <mergeCell ref="AI5:AK5"/>
+    <mergeCell ref="E3:Y3"/>
     <mergeCell ref="B12:B17"/>
     <mergeCell ref="C12:C17"/>
     <mergeCell ref="D7:AB7"/>
@@ -13506,13 +13513,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D8:AB8"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="AI9:AK9"/>
-    <mergeCell ref="AG1:AK1"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="H2:U2"/>
-    <mergeCell ref="D6:AB6"/>
-    <mergeCell ref="AI5:AK5"/>
-    <mergeCell ref="E3:Y3"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
